--- a/Excel Practice @ Day 02.xlsx
+++ b/Excel Practice @ Day 02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MY FILES\M S Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9133C2-4E6F-407A-92D0-B2DAB36C327E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F13646B-7202-4A5D-AE04-6945BF91C2FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{9C0E0D5D-D44B-445C-A246-C8AA0ED14817}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{9C0E0D5D-D44B-445C-A246-C8AA0ED14817}"/>
   </bookViews>
   <sheets>
     <sheet name="Formatting" sheetId="1" r:id="rId1"/>
@@ -7470,20 +7470,20 @@
         <v>111</v>
       </c>
       <c r="I11" s="9">
-        <f>SUM(6:10)</f>
-        <v>144200</v>
+        <f>SUM(I6:I10)</f>
+        <v>24700</v>
       </c>
       <c r="J11" s="9">
-        <f t="shared" ref="J11:L11" si="1">SUM(6:10)</f>
-        <v>144200</v>
+        <f t="shared" ref="J11:L11" si="1">SUM(J6:J10)</f>
+        <v>22700</v>
       </c>
       <c r="K11" s="9">
         <f t="shared" si="1"/>
-        <v>144200</v>
+        <v>24700</v>
       </c>
       <c r="L11" s="9">
         <f t="shared" si="1"/>
-        <v>144200</v>
+        <v>72100</v>
       </c>
     </row>
     <row r="12" spans="8:12" ht="26" x14ac:dyDescent="0.6">
